--- a/02_加值成品/九上/九上4-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上4-1_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上4-1 靜電現象　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國三上學期 九上4-1 靜電現象　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>物體因摩擦而帶電稱？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>摩擦起電</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>負電</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>正電</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>帶電感應</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>起電</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>摩擦起電的原因是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>電子</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>排斥</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>變小</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>電子轉移</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>移動</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>失去電子的物體帶？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>相吸</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>正電</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>庫侖(C)</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>電子</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>失電子</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>得到電子的物體帶？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>相斥</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>負電</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>排斥</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>帶電感應</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>得電子</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>同性電荷會？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>負電</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>相斥</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>電子轉移</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>帶電感應</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>排斥</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>異性電荷會？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>吸引</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>摩擦起電</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>相吸</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>庫侖(C)</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>吸引</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>電量越大電力？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>相斥</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>越大</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>電子轉移</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>帶電感應</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>正比</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>距離越近電力？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>負電</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>相斥</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>庫侖(C)</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>越大</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>越強</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>摩擦起電時發生什麼的轉移？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>相吸</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>電子轉移</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>帶電感應</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>電子</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>電子</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>帶同性電的兩物體會互相？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>庫侖(C)</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>負電</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>電子轉移</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>排斥</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>同性斥</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上4-1 靜電現象　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國三上學期 九上4-1 靜電現象　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>摩擦起電是創造電荷嗎？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>水分少電荷不易導走</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>導走靜電防火花</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>不是,電子轉移</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>帶電梳子使紙屑感應而被吸</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>守恆</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>絲綢摩擦玻璃棒,玻璃棒失電子帶？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>負電</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>相吸</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>正電</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>吸引</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>失電子</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>兩正電荷互相？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>相斥</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>排斥</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>電子轉移</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>變小</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>同性</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>正電與負電互相？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>帶電感應</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>吸引</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>靜電吸附</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>庫侖(C)</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>異性</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>電量單位是？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>負電</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>帶電感應</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>電子轉移</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>庫侖(C)</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>電荷</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>兩帶電體距離拉遠電力？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>靜電吸附</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>增大</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>負電</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>變小</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>距離增</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>影印機利用什麼？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>相吸</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>越大</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>靜電吸附</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>摩擦起電</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>應用</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>油罐車拖鐵鏈接地為了？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>導走靜電防火花</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>被導走中和,金屬導電</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>水分少電荷不易導走</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>不是,電子轉移</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>安全</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>氣球摩擦頭髮後能吸小紙屑因為？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>帶電感應</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>排斥</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>正電</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>摩擦起電</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>靜電</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>得到電子的物體帶何電？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>電子</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>變小</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>負電</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>越大</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>得電子</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上4-1 靜電現象　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國三上學期 九上4-1 靜電現象　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>為何摩擦起電後兩物帶等量異性電？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>被導走中和,金屬導電</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>不是,電子轉移</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>電子由一方轉到另一方,電荷守恆</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>水分少電荷不易導走</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>守恆</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>兩帶電小球電量加倍距離不變電力如何？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>增大</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>庫侖(C)</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>越大</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>相吸</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>電量正比</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>用電性解釋為何梳過頭髮的梳子吸紙屑？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>導走靜電防火花</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>帶電梳子使紙屑感應而被吸</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>使灰塵帶電被異性電極吸附</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>引導電荷入地避免雷擊損害</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>感應</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>避雷針如何保護建築？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>使灰塵帶電被異性電極吸附</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>引導電荷入地避免雷擊損害</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>導走靜電防火花</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>帶電梳子使紙屑感應而被吸</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>應用</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>乾燥天氣易有靜電因為？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>導走靜電防火花</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>水分少電荷不易導走</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>電子由一方轉到另一方,電荷守恆</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>帶電梳子使紙屑感應而被吸</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>條件</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>兩帶電體距離減半電力大致如何？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>正電</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>越大</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>增大</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>摩擦起電</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>距離越近越強</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>靜電除塵器原理？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>被導走中和,金屬導電</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>帶電梳子使紙屑感應而被吸</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>導走靜電防火花</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>使灰塵帶電被異性電極吸附</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>應用</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>帶電體接觸金屬後電荷?為何</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>引導電荷入地避免雷擊損害</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>摩擦起電且乾燥不易導走</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>導走靜電防火花</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>被導走中和,金屬導電</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>導電</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>為何冬天脫毛衣易有靜電火花？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>水分少電荷不易導走</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>電子由一方轉到另一方,電荷守恆</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>摩擦起電且乾燥不易導走</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>使灰塵帶電被異性電極吸附</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>乾燥</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>兩帶電體距離變為2倍電力大致如何？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>變小</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>正電</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>越大</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>摩擦起電</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>距離</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/九上/九上4-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上4-1_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>起電</t>
+          <t>起電：兩個物體互相摩擦後,表面帶上了電,這種現象叫摩擦起電</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>移動</t>
+          <t>移動：摩擦時電子會從一個物體跑到另一個物體上,造成雙方帶電</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>失電子</t>
+          <t>失電子：一個物體的電子被拿走後,正電荷變得比較多,所以帶正電</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>得電子</t>
+          <t>得電子：一個物體多得到了電子,負電荷變得比較多,所以帶負電</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>排斥</t>
+          <t>排斥：帶相同種類電性的兩物體,例如都帶正電,會互相推開</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>吸引</t>
+          <t>吸引：帶不同種類電性的兩物體,例如一正一負,會互相拉近</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>正比</t>
+          <t>正比：帶的電荷量越多,兩物體之間的電力就會跟著變大</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>越強</t>
+          <t>越強：兩個帶電物體靠得越近,它們之間的吸引或排斥力就越強</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>電子</t>
+          <t>電子：兩物體互相摩擦時,電子會從一物體轉移到另一物體上,使兩者分別帶正電與負電</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>同性斥</t>
+          <t>同性斥：電荷有同性相斥、異性相吸的規律,兩個都帶正電或都帶負電的物體會互相排斥</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>守恆</t>
+          <t>守恆：摩擦並沒有生出新的電荷,只是把原本存在的電子從一邊轉到另一邊</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>失電子</t>
+          <t>失電子：玻璃棒在摩擦過程中把電子讓給了絲綢,自己少了電子就帶正電</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>同性</t>
+          <t>同性：兩個都帶正電的物體,電性相同,彼此會互相推開</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>異性</t>
+          <t>異性：一個帶正電一個帶負電,電性不同,彼此會互相吸引靠近</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>電荷</t>
+          <t>電荷：科學上用庫侖這個單位來表示電荷量的多少</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>距離增</t>
+          <t>距離增：兩個帶電物體之間距離變大時,彼此感受到的電力會跟著變小</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>應用</t>
+          <t>應用：影印機利用靜電把碳粉吸附在紙張上,印出文字圖案</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>安全</t>
+          <t>安全：讓車身累積的靜電經由鐵鏈流入地面,避免產生火花引發危險</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>靜電</t>
+          <t>靜電：氣球摩擦後帶了靜電,靠近輕小的紙屑時會使紙屑產生感應電荷,兩者互相吸引而被吸附</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>得電子</t>
+          <t>得電子：電子帶負電,一個物體如果得到(多了)電子,整體就會帶負電</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>守恆</t>
+          <t>守恆：一方少掉的電子數量,剛好等於另一方多得到的電子數量,所以帶的電量一樣多但電性相反</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>電量正比</t>
+          <t>電量正比：距離沒有改變,只要其中一顆球帶的電量變成兩倍,兩者間的電力也會跟著變大</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>感應</t>
+          <t>感應：帶電的梳子靠近紙屑時,會使紙屑表面感應出相反電性,因此互相吸引</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>應用</t>
+          <t>應用：避雷針把雷擊產生的巨大電流引導到地下,不讓電流通過建築物造成損害</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>條件</t>
+          <t>條件：空氣潮濕時水氣能幫忙導走電荷,乾燥時沒有水分帶走,電荷容易累積</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>距離越近越強</t>
+          <t>距離越近越強：兩個帶電體距離縮短一半,彼此之間感受到的電力會明顯變得更大</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>應用</t>
+          <t>應用：先讓灰塵微粒帶上電荷,再用相反電性的電極把這些帶電灰塵吸附下來</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>導電</t>
+          <t>導電：金屬內部電子容易自由移動,帶電體一接觸金屬,電荷就會被導走而中和消失</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>乾燥</t>
+          <t>乾燥：冬天空氣乾燥,衣服摩擦產生的靜電不容易透過潮濕的空氣或皮膚導走,電荷持續累積,脫衣服時瞬間放電就會產生火花</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>距離</t>
+          <t>距離：帶電體之間的靜電力會隨距離增加而變小,距離拉遠時彼此的吸引或排斥力會明顯減弱</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/九上/九上4-1_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上4-1_三種難度測驗卷.xlsx
@@ -603,17 +603,17 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>電子</t>
+          <t>摩擦起電</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>排斥</t>
+          <t>負電</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>變小</t>
+          <t>相吸</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -883,17 +883,17 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>相吸</t>
+          <t>增大</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>電子轉移</t>
+          <t>摩擦起電</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>帶電感應</t>
+          <t>靜電吸附</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
